--- a/output/06.01.26/Tables.xlsx
+++ b/output/06.01.26/Tables.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1555,6 +1555,9 @@
   </si>
   <si>
     <t xml:space="preserve">(861 - 1,438)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cSAD_averted_new.y</t>
   </si>
 </sst>
 </file>
@@ -5633,9 +5636,12 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" t="s">
         <v>500</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5646,10 +5652,13 @@
       <c r="B2" t="n">
         <v>0.00474591236617631</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="n">
         <v>336.1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5660,10 +5669,13 @@
       <c r="B3" t="n">
         <v>0.00399205202312139</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" t="n">
         <v>-475.7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>275</v>
       </c>
     </row>
